--- a/artfynd/A 57983-2025 artfynd.xlsx
+++ b/artfynd/A 57983-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82766075</v>
+        <v>82766074</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606700.0857272703</v>
+        <v>606735</v>
       </c>
       <c r="R2" t="n">
-        <v>6675118.168556738</v>
+        <v>6675110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82766074</v>
+        <v>82766075</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606735.2001823969</v>
+        <v>606700</v>
       </c>
       <c r="R3" t="n">
-        <v>6675110.237650126</v>
+        <v>6675118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>82766076</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606699.8538026882</v>
+        <v>606700</v>
       </c>
       <c r="R4" t="n">
-        <v>6675126.121813271</v>
+        <v>6675126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2019-06-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
